--- a/DATN_HoCaGiay/TAI_VE/DieuTietNam_LapBang_CoTonThat.xlsx
+++ b/DATN_HoCaGiay/TAI_VE/DieuTietNam_LapBang_CoTonThat.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">•  Bước 1 – sheet B1_KhongTonThat: ΔV = W đến − W dùng; tháng thừa (ΔV &gt; 0) hồ tích nước, tháng thiếu (ΔV &lt; 0) hồ cấp nước. Hồ làm việc một lần trong năm (một thời kỳ cấp nước liên tục tháng 12 ÷ 4) nên dung tích hữu ích cần Vhi = tổng lượng thiếu. Quá trình dung tích tính theo cách tích sớm: thừa đến đâu tích đến đó, đầy (Vc + Vhi) thì xả.</t>
   </si>
   <si>
-    <t xml:space="preserve">•  Bước 2 – sheet B2_Lan1: tính tổn thất từ quá trình dung tích của bước 1: V̄ = (V đầu + V cuối)/2 → tra Z̄ (bảng V ~ Z) → F̄ (bảng Z ~ F); W bốc hơi = ΔZ × F̄ (mm ÷ 1000 × km² = 10⁶ m³); W thấm = k_t × V̄; W tổn thất = W bốc hơi + W thấm. Điều tiết lại với W dùng + W tổn thất → Vhi lần 1.</t>
+    <t xml:space="preserve">•  Bước 2 – sheet B2_Lan1: tính tổn thất từ quá trình dung tích của bước 1: Vtb = (V đầu + V cuối)/2 → tra Ztb (bảng V ~ Z) → Ftb (bảng Z ~ F); W bốc hơi = ΔZ × Ftb (mm ÷ 1000 × km² = 10⁶ m³); W thấm = k_t × Vtb; W tổn thất = W bốc hơi + W thấm. Điều tiết lại với W dùng + W tổn thất → Vhi lần 1.</t>
   </si>
   <si>
     <t xml:space="preserve">•  Bước 3, 4 – sheet B3_Lan2, B4_Lan3: tính lại tổn thất theo quá trình dung tích của lần trước và điều tiết lại; dừng khi sai số Vhi giữa hai lần liên tiếp ≤ 1% (thường 2 lần là đạt).</t>
@@ -483,22 +483,22 @@
     <t xml:space="preserve">V cuối tháng (lần trước)</t>
   </si>
   <si>
-    <t xml:space="preserve">V̄ = (V đầu + V cuối)/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z̄ (m) tra V ~ Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F̄ (km²) tra Z ~ F</t>
+    <t xml:space="preserve">Vtb = (V đầu + V cuối)/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ztb (m) tra V ~ Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ftb (km²) tra Z ~ F</t>
   </si>
   <si>
     <t xml:space="preserve">ΔZ bốc hơi (mm)</t>
   </si>
   <si>
-    <t xml:space="preserve">W bốc hơi = ΔZ·F̄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W thấm = k_t·V̄</t>
+    <t xml:space="preserve">W bốc hơi = ΔZ·Ftb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W thấm = k_t·Vtb</t>
   </si>
   <si>
     <t xml:space="preserve">W tổn thất</t>
@@ -1786,11 +1786,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="15802118"/>
-        <c:axId val="93188456"/>
+        <c:axId val="51802485"/>
+        <c:axId val="10426756"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="15802118"/>
+        <c:axId val="51802485"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1856,7 +1856,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93188456"/>
+        <c:crossAx val="10426756"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1864,7 +1864,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93188456"/>
+        <c:axId val="10426756"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="40"/>
@@ -1942,7 +1942,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15802118"/>
+        <c:crossAx val="51802485"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -2527,7 +2527,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
